--- a/result_table_templates/SMSCABella.xlsx
+++ b/result_table_templates/SMSCABella.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\isabe\Documents\Schwartz Lab\GitHub\DJ_schwartzlab\result_table_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964A9838-8221-43F7-BDB9-2439ED4775D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1516A6-E9FF-488B-AFAC-F9B4FE0F35EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,10 +166,10 @@
     <t>spike count in tail time, variance</t>
   </si>
   <si>
-    <t>baseline firing rate (in pre time) for each trial (Hz)</t>
-  </si>
-  <si>
-    <t>baseline_rate_all</t>
+    <t>baseline_rate_var</t>
+  </si>
+  <si>
+    <t>variance in baseline firing rate (in pre time) over all trials (Hz)</t>
   </si>
 </sst>
 </file>
@@ -748,13 +748,13 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
         <v>49</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
